--- a/artfynd/A 31685-2026 artfynd.xlsx
+++ b/artfynd/A 31685-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136461829</v>
       </c>
       <c r="B3" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136461845</v>
       </c>
       <c r="B4" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31685-2026 artfynd.xlsx
+++ b/artfynd/A 31685-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136461829</v>
       </c>
       <c r="B3" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136461845</v>
       </c>
       <c r="B4" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31685-2026 artfynd.xlsx
+++ b/artfynd/A 31685-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136461829</v>
       </c>
       <c r="B3" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136461845</v>
       </c>
       <c r="B4" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31685-2026 artfynd.xlsx
+++ b/artfynd/A 31685-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136461829</v>
       </c>
       <c r="B3" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136461845</v>
       </c>
       <c r="B4" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
